--- a/test_samples/KUEHNE_NAGEL/sample3_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample3_ref.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2550" yWindow="5370" windowWidth="28800" windowHeight="15510" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8055" yWindow="5145" windowWidth="28800" windowHeight="15315" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -83,7 +83,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -106,6 +106,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -503,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="17.375" customWidth="1" style="7" min="1" max="1"/>
@@ -524,312 +527,212 @@
     <col width="13.375" customWidth="1" style="7" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>帳單辨識指引: 有時候PDF會混合印尼稅務發票, 帳單辨識請以右上角或是右下角有Kuehne Nagel字樣為主, 才是Kuehne Nagel正確帳單格式 (所有國家的 Kuehne Nagel帳單都適用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>只有一個TOTAL的VAT, 所有費用項目金額加上VAT金額= 總金額 (Amount Due這個欄位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>右下角欄位</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>INVOICE TO</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>VAT AMOUNTS</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>DESCRIPTION OF GOODS PO NO.</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>ETA/ATA</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>ETD/ATD</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>KN TRACKING NO.</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>P. OF LOADING</t>
+        </is>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>P. OF DISCHARGE</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>QTY TYPE</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t>VESSEL NAME VOYAGE</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>MARKS &amp; NOS</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t>SHIPPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>INVOICE DATE
 發票日期</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>INVOICE NO
 發票號碼</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>SUPPLIER
 供應商名稱</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>CONSIGNEE
 集團公司名稱</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Description
 費用名稱</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>AMOUNT
 金額</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Order No.</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Arrive Date
 到達日</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>on board date
 開船日</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>B/L NO.
 提單號碼</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>MBL NO.
 主提單號碼</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Port of Loading
 啟運港</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Port of discharge
 目的港</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Volume
 材積</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Vessel
 船名</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Container no.
 貨櫃號碼</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Shipper
 出貨方</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>JKT1521476</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>KUEHNE NAGEL INDONESIA</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>PT. POU CHEN INDONESIA</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>SECURITY FILING</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>46286</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>1076285746</v>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>JAKARTA</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>TOKYO</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>VANCOUVER 058N</t>
-        </is>
-      </c>
-      <c r="Q2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>JKT1521476</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>KUEHNE NAGEL INDONESIA</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>PT. POU CHEN INDONESIA</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>B/L FEE EXPORT</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>46286</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>1076285746</v>
-      </c>
-      <c r="L3" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M3" s="0" t="inlineStr">
-        <is>
-          <t>JAKARTA</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>TOKYO</t>
-        </is>
-      </c>
-      <c r="P3" s="0" t="inlineStr">
-        <is>
-          <t>VANCOUVER 058N</t>
-        </is>
-      </c>
-      <c r="Q3" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R3" s="0" t="inlineStr">
-        <is>
-          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>JKT1521476</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>KUEHNE NAGEL INDONESIA</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>PT. POU CHEN INDONESIA</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>HANDLING / DOCUMENTATION FEE EXPORT</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>46286</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>1076285746</v>
-      </c>
-      <c r="L4" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t>JAKARTA</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>TOKYO</t>
-        </is>
-      </c>
-      <c r="P4" s="0" t="inlineStr">
-        <is>
-          <t>VANCOUVER 058N</t>
-        </is>
-      </c>
-      <c r="Q4" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="0" t="inlineStr">
-        <is>
-          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -854,11 +757,16 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>MANIFEST FEE ORIGIN</t>
+          <t>SECURITY FILING</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>550000</v>
+        <v>700000</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I5" s="5" t="n">
         <v>46294</v>
@@ -884,6 +792,11 @@
           <t>TOKYO</t>
         </is>
       </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
           <t>VANCOUVER 058N</t>
@@ -891,7 +804,7 @@
       </c>
       <c r="Q5" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R5" s="0" t="inlineStr">
@@ -921,11 +834,16 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>VGM FEE</t>
+          <t>B/L FEE EXPORT</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>684000</v>
+        <v>640000</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I6" s="5" t="n">
         <v>46294</v>
@@ -951,6 +869,11 @@
           <t>TOKYO</t>
         </is>
       </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
           <t>VANCOUVER 058N</t>
@@ -958,7 +881,7 @@
       </c>
       <c r="Q6" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R6" s="0" t="inlineStr">
@@ -988,11 +911,16 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>SEAL PROVISION FEE</t>
+          <t>HANDLING / DOCUMENTATION FEE EXPORT</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>720000</v>
+        <v>640000</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I7" s="5" t="n">
         <v>46294</v>
@@ -1018,6 +946,11 @@
           <t>TOKYO</t>
         </is>
       </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
           <t>VANCOUVER 058N</t>
@@ -1025,7 +958,7 @@
       </c>
       <c r="Q7" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R7" s="0" t="inlineStr">
@@ -1055,11 +988,16 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>THC - ORIGIN</t>
+          <t>MANIFEST FEE ORIGIN</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7173967</v>
+        <v>550000</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I8" s="5" t="n">
         <v>46294</v>
@@ -1085,6 +1023,11 @@
           <t>TOKYO</t>
         </is>
       </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
           <t>VANCOUVER 058N</t>
@@ -1092,7 +1035,7 @@
       </c>
       <c r="Q8" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R8" s="0" t="inlineStr">
@@ -1122,11 +1065,16 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>CONTAINER POSITIONING EXPORT</t>
+          <t>VGM FEE</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>428575</v>
+        <v>684000</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I9" s="5" t="n">
         <v>46294</v>
@@ -1154,7 +1102,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>1X40GE</t>
+          <t>1X40G+1X40H+1X20G</t>
         </is>
       </c>
       <c r="P9" s="0" t="inlineStr">
@@ -1164,7 +1112,7 @@
       </c>
       <c r="Q9" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R9" s="0" t="inlineStr">
@@ -1194,11 +1142,16 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>CONTAINER POSITIONING EXPORT</t>
+          <t>SEAL PROVISION FEE</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>428575</v>
+        <v>720000</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I10" s="5" t="n">
         <v>46294</v>
@@ -1226,7 +1179,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>1X40HC</t>
+          <t>1X40G+1X40H+1X20G</t>
         </is>
       </c>
       <c r="P10" s="0" t="inlineStr">
@@ -1236,7 +1189,7 @@
       </c>
       <c r="Q10" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R10" s="0" t="inlineStr">
@@ -1266,11 +1219,16 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>CONTAINER POSITIONING EXPORT</t>
+          <t>THC - ORIGIN</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>279505</v>
+        <v>7173967</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I11" s="5" t="n">
         <v>46294</v>
@@ -1298,7 +1256,7 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>1X20GE</t>
+          <t>1X40G+1X40H+1X20G</t>
         </is>
       </c>
       <c r="P11" s="0" t="inlineStr">
@@ -1308,7 +1266,7 @@
       </c>
       <c r="Q11" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
         </is>
       </c>
       <c r="R11" s="0" t="inlineStr">
@@ -1336,8 +1294,18 @@
           <t>PT. POU CHEN INDONESIA</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>1346908</v>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>CONTAINER POSITIONING EXPORT</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>428575</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
       </c>
       <c r="I12" s="5" t="n">
         <v>46294</v>
@@ -1363,6 +1331,11 @@
           <t>TOKYO</t>
         </is>
       </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
           <t>VANCOUVER 058N</t>
@@ -1370,52 +1343,283 @@
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>JKT1521476</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU CHEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>CONTAINER POSITIONING EXPORT</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>428575</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>1076285746</v>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R12" s="0" t="inlineStr">
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>TOKYO</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="inlineStr">
+        <is>
+          <t>VANCOUVER 058N</t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="inlineStr">
+        <is>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
         <is>
           <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="R13" s="1" t="n"/>
-    </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>JKT1521476</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU CHEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>CONTAINER POSITIONING EXPORT</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>279505</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>1076285746</v>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>TOKYO</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="inlineStr">
+        <is>
+          <t>VANCOUVER 058N</t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="inlineStr">
+        <is>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="N15" s="6" t="n"/>
+      <c r="A15" s="5" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>JKT1521476</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU CHEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1346908</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>1076285746</v>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>TOKYO</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>1X40G+1X40H+1X20G</t>
+        </is>
+      </c>
+      <c r="P15" s="0" t="inlineStr">
+        <is>
+          <t>VANCOUVER 058N</t>
+        </is>
+      </c>
+      <c r="Q15" s="0" t="inlineStr">
+        <is>
+          <t>FSCU5030780, OOCU9577099, MAGU2272975</t>
+        </is>
+      </c>
+      <c r="R15" s="0" t="inlineStr">
+        <is>
+          <t>THE LOOK (MACAO COMMERCIAL OFFSHORE COMPANY LIMITED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="N16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="N17" s="6" t="n"/>
-    </row>
+      <c r="R16" s="1" t="n"/>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
+      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23">
-      <c r="R23" s="1" t="n"/>
+      <c r="N19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="N20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="R26" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test_samples/KUEHNE_NAGEL/sample3_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample3_ref.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I12" s="5" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>4501208511, 4501208622, 4501208514, 4501208502, 4501208568, 4501208620, 4501208509</t>
+          <t>4501208511,4501208622,4501208514,4501208502,4501208568,4501208620,4501208509</t>
         </is>
       </c>
       <c r="I15" s="5" t="n">
